--- a/PLANTILLA_CAJA_CHICA_NOVICOMPU.xlsx
+++ b/PLANTILLA_CAJA_CHICA_NOVICOMPU.xlsx
@@ -3466,7 +3466,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="IHxYi4ae1SewgmcoVEZzVOMEKKxp2DWeJLE0JTveJ8uQ7q5AifH4gyFCV4nRcMFqCjiEFR6GCorVEKCBvEqKyg==" saltValue="D9RAi0chDdzCPdZ1H6oyfA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
